--- a/docs/StructureDefinition-BRImunobiologicoAdministrado-3.0.xlsx
+++ b/docs/StructureDefinition-BRImunobiologicoAdministrado-3.0.xlsx
@@ -374,7 +374,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -621,7 +621,7 @@
     <t>The reason why a vaccine was not administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -933,7 +933,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1011,7 +1011,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1096,7 +1096,7 @@
     <t>Immunization.patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1136,7 +1136,7 @@
     <t>Immunization.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1247,7 +1247,7 @@
     <t>Immunization.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1585,7 +1585,7 @@
     <t>Immunization.doseQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1774,7 +1774,7 @@
     <t>The reason why a vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1830,7 +1830,7 @@
     <t>The reason why a dose is considered to be subpotent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason|4.0.1</t>
   </si>
   <si>
     <t>Immunization.education</t>
@@ -1912,7 +1912,7 @@
     <t>The patient's eligibility for a vaccation program.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility|4.0.1</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = 64994-7</t>
@@ -1930,7 +1930,7 @@
     <t>The source of funding used to purchase the vaccine administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source|4.0.1</t>
   </si>
   <si>
     <t>Immunization.reaction</t>
@@ -1975,7 +1975,7 @@
     <t>Immunization.reaction.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -2236,7 +2236,7 @@
     <t>The vaccine preventable disease the dose is being administered for.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease|4.0.1</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]</t>
@@ -2754,7 +2754,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>175</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>196</v>
       </c>
@@ -5907,7 +5907,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>273</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>368</v>
       </c>
@@ -9994,7 +9994,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>422</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>432</v>
       </c>
@@ -12453,7 +12453,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>448</v>
       </c>
@@ -12572,7 +12572,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>452</v>
       </c>
@@ -13038,7 +13038,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>460</v>
       </c>
@@ -13268,7 +13268,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>471</v>
       </c>
@@ -14674,7 +14674,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>489</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
         <v>513</v>
       </c>
@@ -18065,7 +18065,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
         <v>544</v>
       </c>
@@ -21430,7 +21430,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="162" hidden="true">
+    <row r="162">
       <c r="A162" t="s" s="2">
         <v>645</v>
       </c>
@@ -21773,7 +21773,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>650</v>
       </c>
@@ -24682,7 +24682,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="190" hidden="true">
+    <row r="190">
       <c r="A190" t="s" s="2">
         <v>721</v>
       </c>
@@ -24918,12 +24918,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO191">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
